--- a/movies.xlsx
+++ b/movies.xlsx
@@ -38168,7 +38168,7 @@
       </c>
       <c r="F944" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>449</t>
         </is>
       </c>
       <c r="G944" t="inlineStr">
